--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +108,15 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>course.TbCourse</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>course.xlsx</t>
   </si>
   <si>
     <t>item.TbItem</t>
@@ -109,7 +131,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -120,14 +142,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -135,7 +157,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -143,14 +165,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -158,7 +180,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -166,7 +188,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +196,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -182,7 +204,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -190,14 +212,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -205,7 +227,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -213,7 +235,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -221,14 +243,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -236,35 +258,35 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -728,55 +750,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1045,13 +1067,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="20.3809523809524" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="32.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="24.3809523809524" customWidth="1"/>
+    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.575" customWidth="1"/>
+    <col min="4" max="4" width="32.425" customWidth="1"/>
+    <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1157,6 +1179,20 @@
       </c>
       <c r="E4" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="2:5">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>course.xlsx</t>
+  </si>
+  <si>
+    <t>global.TbGlobal</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>global.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
   </si>
   <si>
     <t>item.TbItem</t>
@@ -1067,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1181,7 +1193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" customFormat="1" spans="2:7">
       <c r="B5" t="s">
         <v>30</v>
       </c>
@@ -1193,6 +1205,23 @@
       </c>
       <c r="E5" t="s">
         <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:5">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -110,13 +110,13 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>course.TbCourse</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>course.xlsx</t>
+    <t>game_event.TbGameEvent</t>
+  </si>
+  <si>
+    <t>GameEvent</t>
+  </si>
+  <si>
+    <t>game_event.xlsx</t>
   </si>
   <si>
     <t>global.TbGlobal</t>
@@ -1082,7 +1082,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
     <col min="4" max="4" width="32.425" customWidth="1"/>
     <col min="5" max="5" width="24.3833333333333" customWidth="1"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -110,19 +110,28 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>game_event.TbGameEvent</t>
-  </si>
-  <si>
-    <t>GameEvent</t>
-  </si>
-  <si>
-    <t>game_event.xlsx</t>
-  </si>
-  <si>
-    <t>global.TbGlobal</t>
-  </si>
-  <si>
-    <t>Global</t>
+    <t>TbEffect</t>
+  </si>
+  <si>
+    <t>EffectRow</t>
+  </si>
+  <si>
+    <t>effect.xlsx</t>
+  </si>
+  <si>
+    <t>TbEvent</t>
+  </si>
+  <si>
+    <t>EventRow</t>
+  </si>
+  <si>
+    <t>event.xlsx</t>
+  </si>
+  <si>
+    <t>TbGlobal</t>
+  </si>
+  <si>
+    <t>GlobalRow</t>
   </si>
   <si>
     <t>global.xlsx</t>
@@ -131,10 +140,10 @@
     <t>one</t>
   </si>
   <si>
-    <t>item.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
+    <t>TbItem</t>
+  </si>
+  <si>
+    <t>ItemRow</t>
   </si>
   <si>
     <t>item.xlsx</t>
@@ -1079,8 +1088,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1179,7 +1188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" customFormat="1" spans="2:5">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:7">
+    <row r="5" customFormat="1" spans="2:5">
       <c r="B5" t="s">
         <v>30</v>
       </c>
@@ -1206,22 +1215,36 @@
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" customFormat="1" spans="2:7">
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" spans="2:5">
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:5">
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -110,13 +110,13 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbEffect</t>
-  </si>
-  <si>
-    <t>EffectRow</t>
-  </si>
-  <si>
-    <t>effect.xlsx</t>
+    <t>TbDialogue</t>
+  </si>
+  <si>
+    <t>DialogueRow</t>
+  </si>
+  <si>
+    <t>dialogue.xlsx</t>
   </si>
   <si>
     <t>TbEvent</t>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -110,22 +110,31 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbDialogue</t>
-  </si>
-  <si>
-    <t>DialogueRow</t>
-  </si>
-  <si>
-    <t>dialogue.xlsx</t>
-  </si>
-  <si>
-    <t>TbEvent</t>
-  </si>
-  <si>
-    <t>EventRow</t>
-  </si>
-  <si>
-    <t>event.xlsx</t>
+    <t>TbGameplayGraph</t>
+  </si>
+  <si>
+    <t>GameplayGraphRow</t>
+  </si>
+  <si>
+    <t>gameplay_graph.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameplayNode</t>
+  </si>
+  <si>
+    <t>GameplayNodeRow</t>
+  </si>
+  <si>
+    <t>gameplay_node.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameplayGraphTrigger</t>
+  </si>
+  <si>
+    <t>GameplayGraphTriggerRow</t>
+  </si>
+  <si>
+    <t>gameplay_graph_trigger.xlsx</t>
   </si>
   <si>
     <t>TbGlobal</t>
@@ -159,43 +168,36 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -203,15 +205,13 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -219,7 +219,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -227,7 +226,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -235,81 +233,64 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -369,19 +350,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,19 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,19 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,19 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,19 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,7 +524,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,10 +673,10 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -704,10 +685,10 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,10 +697,10 @@
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,10 +709,10 @@
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,10 +721,10 @@
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,10 +733,10 @@
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,7 +802,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -874,73 +1069,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -952,23 +1087,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -978,23 +1113,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1002,26 +1137,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1056,17 +1188,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1088,8 +1220,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1216,7 +1348,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:7">
+    <row r="6" customFormat="1" spans="2:5">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -1229,27 +1361,40 @@
       <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" spans="2:5">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,15 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>TbCharacter</t>
+  </si>
+  <si>
+    <t>CharacterRow</t>
+  </si>
+  <si>
+    <t>character.xlsx</t>
   </si>
   <si>
     <t>TbGameplayGraph</t>
@@ -1220,11 +1229,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.75" customWidth="1"/>
-    <col min="3" max="3" width="15.575" customWidth="1"/>
+    <col min="3" max="3" width="22.125" customWidth="1"/>
     <col min="4" max="4" width="32.425" customWidth="1"/>
     <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
@@ -1362,7 +1371,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" customFormat="1" spans="2:5">
       <c r="B7" t="s">
         <v>36</v>
       </c>
@@ -1375,22 +1384,36 @@
       <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="G7" t="s">
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
